--- a/etf_holdings/2026-10-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:03</t>
+          <t>2026-10-26 23:28:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:15</t>
+          <t>2026-10-26 23:28:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:26</t>
+          <t>2026-10-26 23:28:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-26 23:19:38</t>
+          <t>2026-10-26 23:28:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
